--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.2969</v>
+      </c>
+      <c r="G2" t="n">
+        <v>151.0448</v>
+      </c>
+      <c r="H2" t="n">
+        <v>404.7857</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9885</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.3176</v>
+      </c>
+      <c r="G3" t="n">
+        <v>146.0298</v>
+      </c>
+      <c r="H3" t="n">
+        <v>418.6153</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.3879</v>
+      </c>
+      <c r="G4" t="n">
+        <v>167.9224</v>
+      </c>
+      <c r="H4" t="n">
+        <v>462.6603</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8154</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.9867</v>
+      </c>
+      <c r="G5" t="n">
+        <v>466.8552</v>
+      </c>
+      <c r="H5" t="n">
+        <v>737.8918</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.9649</v>
+      </c>
+      <c r="G6" t="n">
+        <v>464.6835</v>
+      </c>
+      <c r="H6" t="n">
+        <v>729.6925</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.4082</v>
+      </c>
+      <c r="G7" t="n">
+        <v>191.6005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>474.5844</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9704</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.4233</v>
+      </c>
+      <c r="G8" t="n">
+        <v>193.6418</v>
+      </c>
+      <c r="H8" t="n">
+        <v>483.3017</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9823</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.2928</v>
+      </c>
+      <c r="G9" t="n">
+        <v>167.0875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>401.9541</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.4429</v>
+      </c>
+      <c r="G10" t="n">
+        <v>163.8578</v>
+      </c>
+      <c r="H10" t="n">
+        <v>494.3625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9291</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.4424</v>
+      </c>
+      <c r="G11" t="n">
+        <v>285.0217</v>
+      </c>
+      <c r="H11" t="n">
+        <v>494.101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.4417</v>
+      </c>
+      <c r="G12" t="n">
+        <v>285.0983</v>
+      </c>
+      <c r="H12" t="n">
+        <v>493.7026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9391</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.4441</v>
+      </c>
+      <c r="G13" t="n">
+        <v>265.9858</v>
+      </c>
+      <c r="H13" t="n">
+        <v>495.0347</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9283</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.4427</v>
+      </c>
+      <c r="G14" t="n">
+        <v>286.1997</v>
+      </c>
+      <c r="H14" t="n">
+        <v>494.2503</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="G15" t="n">
+        <v>285.0607</v>
+      </c>
+      <c r="H15" t="n">
+        <v>494.4172</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9288</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.4426</v>
+      </c>
+      <c r="G16" t="n">
+        <v>285.1617</v>
+      </c>
+      <c r="H16" t="n">
+        <v>494.2206</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9278999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.4429</v>
+      </c>
+      <c r="G17" t="n">
+        <v>286.7732</v>
+      </c>
+      <c r="H17" t="n">
+        <v>494.3753</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.3067</v>
+      </c>
+      <c r="G18" t="n">
+        <v>141.3703</v>
+      </c>
+      <c r="H18" t="n">
+        <v>411.4052</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.3079</v>
+      </c>
+      <c r="G19" t="n">
+        <v>138.7135</v>
+      </c>
+      <c r="H19" t="n">
+        <v>412.1816</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2969</v>
+      </c>
+      <c r="G20" t="n">
+        <v>142.464</v>
+      </c>
+      <c r="H20" t="n">
+        <v>404.7815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2945</v>
+      </c>
+      <c r="G21" t="n">
+        <v>138.6819</v>
+      </c>
+      <c r="H21" t="n">
+        <v>403.1424</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.2908</v>
+      </c>
+      <c r="G22" t="n">
+        <v>138.8886</v>
+      </c>
+      <c r="H22" t="n">
+        <v>400.5622</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.2949</v>
+      </c>
+      <c r="G23" t="n">
+        <v>142.2974</v>
+      </c>
+      <c r="H23" t="n">
+        <v>403.3844</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.3042</v>
+      </c>
+      <c r="G24" t="n">
+        <v>144.5674</v>
+      </c>
+      <c r="H24" t="n">
+        <v>409.7005</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>143.795</v>
+      </c>
+      <c r="H25" t="n">
+        <v>406.8922</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.3017</v>
+      </c>
+      <c r="G26" t="n">
+        <v>136.8078</v>
+      </c>
+      <c r="H26" t="n">
+        <v>408.0235</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.3121</v>
+      </c>
+      <c r="G27" t="n">
+        <v>144.5872</v>
+      </c>
+      <c r="H27" t="n">
+        <v>415.0324</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.3067</v>
+      </c>
+      <c r="G28" t="n">
+        <v>136.8713</v>
+      </c>
+      <c r="H28" t="n">
+        <v>411.3966</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.3101</v>
+      </c>
+      <c r="G29" t="n">
+        <v>161.4232</v>
+      </c>
+      <c r="H29" t="n">
+        <v>413.6655</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="G30" t="n">
+        <v>165.5457</v>
+      </c>
+      <c r="H30" t="n">
+        <v>409.9493</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.3007</v>
+      </c>
+      <c r="G31" t="n">
+        <v>141.6466</v>
+      </c>
+      <c r="H31" t="n">
+        <v>407.3619</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.3014</v>
+      </c>
+      <c r="G32" t="n">
+        <v>139.7082</v>
+      </c>
+      <c r="H32" t="n">
+        <v>407.7976</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.2995</v>
+      </c>
+      <c r="G33" t="n">
+        <v>138.5481</v>
+      </c>
+      <c r="H33" t="n">
+        <v>406.513</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.3572</v>
+      </c>
+      <c r="G34" t="n">
+        <v>155.2315</v>
+      </c>
+      <c r="H34" t="n">
+        <v>443.9462</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3408</v>
+      </c>
+      <c r="G35" t="n">
+        <v>146.2623</v>
+      </c>
+      <c r="H35" t="n">
+        <v>433.6415</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.3081</v>
+      </c>
+      <c r="G36" t="n">
+        <v>144.3525</v>
+      </c>
+      <c r="H36" t="n">
+        <v>412.3493</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.2979</v>
+      </c>
+      <c r="G37" t="n">
+        <v>171.108</v>
+      </c>
+      <c r="H37" t="n">
+        <v>405.4825</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="G38" t="n">
+        <v>137.0224</v>
+      </c>
+      <c r="H38" t="n">
+        <v>400.7396</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.2924</v>
+      </c>
+      <c r="G39" t="n">
+        <v>144.6516</v>
+      </c>
+      <c r="H39" t="n">
+        <v>401.6865</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.2866</v>
+      </c>
+      <c r="G40" t="n">
+        <v>144.7637</v>
+      </c>
+      <c r="H40" t="n">
+        <v>397.671</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.3581</v>
+      </c>
+      <c r="G41" t="n">
+        <v>154.7251</v>
+      </c>
+      <c r="H41" t="n">
+        <v>444.5496</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.3417</v>
+      </c>
+      <c r="G42" t="n">
+        <v>146.5081</v>
+      </c>
+      <c r="H42" t="n">
+        <v>434.2128</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="G43" t="n">
+        <v>143.5189</v>
+      </c>
+      <c r="H43" t="n">
+        <v>412.937</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.2947</v>
+      </c>
+      <c r="G44" t="n">
+        <v>170.2936</v>
+      </c>
+      <c r="H44" t="n">
+        <v>403.2844</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.2918</v>
+      </c>
+      <c r="G45" t="n">
+        <v>137.114</v>
+      </c>
+      <c r="H45" t="n">
+        <v>401.2891</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.2932</v>
+      </c>
+      <c r="G46" t="n">
+        <v>145.0911</v>
+      </c>
+      <c r="H46" t="n">
+        <v>402.2137</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.2852</v>
+      </c>
+      <c r="G47" t="n">
+        <v>151.9777</v>
+      </c>
+      <c r="H47" t="n">
+        <v>396.7468</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.3196</v>
+      </c>
+      <c r="G48" t="n">
+        <v>150.0634</v>
+      </c>
+      <c r="H48" t="n">
+        <v>419.9648</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.3011</v>
+      </c>
+      <c r="G49" t="n">
+        <v>143.4427</v>
+      </c>
+      <c r="H49" t="n">
+        <v>407.6489</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9301</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.8236</v>
+      </c>
+      <c r="G50" t="n">
+        <v>352.6602</v>
+      </c>
+      <c r="H50" t="n">
+        <v>674.1663</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.8737</v>
+      </c>
+      <c r="G51" t="n">
+        <v>432.7913</v>
+      </c>
+      <c r="H51" t="n">
+        <v>694.3619</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.8722</v>
+      </c>
+      <c r="G52" t="n">
+        <v>253.2649</v>
+      </c>
+      <c r="H52" t="n">
+        <v>693.7646999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9739</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.8533</v>
+      </c>
+      <c r="G53" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>686.2117</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.8369</v>
+      </c>
+      <c r="G54" t="n">
+        <v>374.3873</v>
+      </c>
+      <c r="H54" t="n">
+        <v>679.5921</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9092</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.9067</v>
+      </c>
+      <c r="G55" t="n">
+        <v>413.3794</v>
+      </c>
+      <c r="H55" t="n">
+        <v>707.3315</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.9141</v>
+      </c>
+      <c r="G56" t="n">
+        <v>256.6694</v>
+      </c>
+      <c r="H56" t="n">
+        <v>710.2431</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.9093</v>
+      </c>
+      <c r="G57" t="n">
+        <v>404.1177</v>
+      </c>
+      <c r="H57" t="n">
+        <v>708.3645</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.9752</v>
+      </c>
+      <c r="G58" t="n">
+        <v>461.5699</v>
+      </c>
+      <c r="H58" t="n">
+        <v>733.5714</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8248</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.9691</v>
+      </c>
+      <c r="G59" t="n">
+        <v>460.0352</v>
+      </c>
+      <c r="H59" t="n">
+        <v>731.2899</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8256</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.9695</v>
+      </c>
+      <c r="G60" t="n">
+        <v>460.9157</v>
+      </c>
+      <c r="H60" t="n">
+        <v>731.4295</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8242</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.9706</v>
+      </c>
+      <c r="G61" t="n">
+        <v>460.2261</v>
+      </c>
+      <c r="H61" t="n">
+        <v>731.8599</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.9196</v>
+      </c>
+      <c r="G62" t="n">
+        <v>422.9497</v>
+      </c>
+      <c r="H62" t="n">
+        <v>712.3815</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.9077</v>
+      </c>
+      <c r="G63" t="n">
+        <v>469.1378</v>
+      </c>
+      <c r="H63" t="n">
+        <v>707.7419</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.9141</v>
+      </c>
+      <c r="G64" t="n">
+        <v>469.5093</v>
+      </c>
+      <c r="H64" t="n">
+        <v>710.25</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8244</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.9211</v>
+      </c>
+      <c r="G65" t="n">
+        <v>470.1753</v>
+      </c>
+      <c r="H65" t="n">
+        <v>712.9307</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9500999999999999</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.9158</v>
+      </c>
+      <c r="G66" t="n">
+        <v>324.3285</v>
+      </c>
+      <c r="H66" t="n">
+        <v>710.8966</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="G67" t="n">
+        <v>431.4987</v>
+      </c>
+      <c r="H67" t="n">
+        <v>709.819</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.9164</v>
+      </c>
+      <c r="G68" t="n">
+        <v>312.2426</v>
+      </c>
+      <c r="H68" t="n">
+        <v>711.1324</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.3022</v>
+      </c>
+      <c r="G69" t="n">
+        <v>150.4635</v>
+      </c>
+      <c r="H69" t="n">
+        <v>408.3429</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.2841</v>
+      </c>
+      <c r="G70" t="n">
+        <v>157.9104</v>
+      </c>
+      <c r="H70" t="n">
+        <v>395.9731</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.3144</v>
+      </c>
+      <c r="G71" t="n">
+        <v>147.7907</v>
+      </c>
+      <c r="H71" t="n">
+        <v>416.5199</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.2892</v>
+      </c>
+      <c r="G72" t="n">
+        <v>141.3213</v>
+      </c>
+      <c r="H72" t="n">
+        <v>399.48</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="G73" t="n">
+        <v>173.3679</v>
+      </c>
+      <c r="H73" t="n">
+        <v>436.3506</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="G74" t="n">
+        <v>147.4815</v>
+      </c>
+      <c r="H74" t="n">
+        <v>423.4993</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="G75" t="n">
+        <v>152.3315</v>
+      </c>
+      <c r="H75" t="n">
+        <v>450.9167</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="G76" t="n">
+        <v>152.3315</v>
+      </c>
+      <c r="H76" t="n">
+        <v>450.9167</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.9101</v>
+      </c>
+      <c r="G77" t="n">
+        <v>442.5775</v>
+      </c>
+      <c r="H77" t="n">
+        <v>708.6772</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.9141</v>
+      </c>
+      <c r="G78" t="n">
+        <v>447.6067</v>
+      </c>
+      <c r="H78" t="n">
+        <v>710.2478</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.9166</v>
+      </c>
+      <c r="G79" t="n">
+        <v>448.542</v>
+      </c>
+      <c r="H79" t="n">
+        <v>711.2006</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8484</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.916</v>
+      </c>
+      <c r="G80" t="n">
+        <v>446.8932</v>
+      </c>
+      <c r="H80" t="n">
+        <v>710.9596</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8941</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.9059</v>
+      </c>
+      <c r="G81" t="n">
+        <v>418.4462</v>
+      </c>
+      <c r="H81" t="n">
+        <v>707.0528</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.9036</v>
+      </c>
+      <c r="G82" t="n">
+        <v>376.5176</v>
+      </c>
+      <c r="H82" t="n">
+        <v>706.1334000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.3676</v>
+      </c>
+      <c r="G83" t="n">
+        <v>152.3356</v>
+      </c>
+      <c r="H83" t="n">
+        <v>450.3713</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="G84" t="n">
+        <v>151.8918</v>
+      </c>
+      <c r="H84" t="n">
+        <v>450.2881</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="G85" t="n">
+        <v>152.9954</v>
+      </c>
+      <c r="H85" t="n">
+        <v>451.2231</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.3083</v>
+      </c>
+      <c r="G86" t="n">
+        <v>143.5673</v>
+      </c>
+      <c r="H86" t="n">
+        <v>412.4611</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.3046</v>
+      </c>
+      <c r="G87" t="n">
+        <v>156.9673</v>
+      </c>
+      <c r="H87" t="n">
+        <v>409.9681</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.2984</v>
+      </c>
+      <c r="G88" t="n">
+        <v>137.8008</v>
+      </c>
+      <c r="H88" t="n">
+        <v>405.7758</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G89" t="n">
+        <v>141.0164</v>
+      </c>
+      <c r="H89" t="n">
+        <v>412.2911</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.3092</v>
+      </c>
+      <c r="G90" t="n">
+        <v>143.6677</v>
+      </c>
+      <c r="H90" t="n">
+        <v>413.0624</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.2947</v>
+      </c>
+      <c r="G91" t="n">
+        <v>170.2936</v>
+      </c>
+      <c r="H91" t="n">
+        <v>403.2827</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.2984</v>
+      </c>
+      <c r="G92" t="n">
+        <v>137.8008</v>
+      </c>
+      <c r="H92" t="n">
+        <v>405.7758</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.2947</v>
+      </c>
+      <c r="G93" t="n">
+        <v>170.2936</v>
+      </c>
+      <c r="H93" t="n">
+        <v>403.2827</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.3879</v>
+      </c>
+      <c r="G94" t="n">
+        <v>167.9224</v>
+      </c>
+      <c r="H94" t="n">
+        <v>462.6603</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.0797</v>
+      </c>
+      <c r="G95" t="n">
+        <v>378.3759</v>
+      </c>
+      <c r="H95" t="n">
+        <v>771.8746</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.393</v>
+      </c>
+      <c r="G96" t="n">
+        <v>167.8609</v>
+      </c>
+      <c r="H96" t="n">
+        <v>465.708</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9811</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.3894</v>
+      </c>
+      <c r="G97" t="n">
+        <v>168.1098</v>
+      </c>
+      <c r="H97" t="n">
+        <v>463.5503</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="G98" t="n">
+        <v>143.7823</v>
+      </c>
+      <c r="H98" t="n">
+        <v>408.251</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9789</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.2828</v>
+      </c>
+      <c r="G99" t="n">
+        <v>163.5888</v>
+      </c>
+      <c r="H99" t="n">
+        <v>395.0298</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.3075</v>
+      </c>
+      <c r="G100" t="n">
+        <v>165.7757</v>
+      </c>
+      <c r="H100" t="n">
+        <v>411.9262</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.3028</v>
+      </c>
+      <c r="G101" t="n">
+        <v>173.8032</v>
+      </c>
+      <c r="H101" t="n">
+        <v>408.7666</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.3069</v>
+      </c>
+      <c r="G102" t="n">
+        <v>149.5473</v>
+      </c>
+      <c r="H102" t="n">
+        <v>411.5037</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.3207</v>
+      </c>
+      <c r="G103" t="n">
+        <v>149.4075</v>
+      </c>
+      <c r="H103" t="n">
+        <v>420.7085</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.3038</v>
+      </c>
+      <c r="G104" t="n">
+        <v>151.8478</v>
+      </c>
+      <c r="H104" t="n">
+        <v>409.4548</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.2937</v>
+      </c>
+      <c r="G105" t="n">
+        <v>145.5803</v>
+      </c>
+      <c r="H105" t="n">
+        <v>402.5937</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.2764</v>
+      </c>
+      <c r="G106" t="n">
+        <v>140.4119</v>
+      </c>
+      <c r="H106" t="n">
+        <v>390.5261</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9786</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.2864</v>
+      </c>
+      <c r="G107" t="n">
+        <v>165.4651</v>
+      </c>
+      <c r="H107" t="n">
+        <v>397.5491</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.3819</v>
+      </c>
+      <c r="G108" t="n">
+        <v>189.3776</v>
+      </c>
+      <c r="H108" t="n">
+        <v>459.0692</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.3478</v>
+      </c>
+      <c r="G109" t="n">
+        <v>153.1223</v>
+      </c>
+      <c r="H109" t="n">
+        <v>438.1152</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.3108</v>
+      </c>
+      <c r="G110" t="n">
+        <v>141.9579</v>
+      </c>
+      <c r="H110" t="n">
+        <v>414.1135</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.3128</v>
+      </c>
+      <c r="G111" t="n">
+        <v>143.9735</v>
+      </c>
+      <c r="H111" t="n">
+        <v>415.4574</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.3813</v>
+      </c>
+      <c r="G112" t="n">
+        <v>188.8464</v>
+      </c>
+      <c r="H112" t="n">
+        <v>458.684</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.3494</v>
+      </c>
+      <c r="G113" t="n">
+        <v>152.8505</v>
+      </c>
+      <c r="H113" t="n">
+        <v>439.09</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.3085</v>
+      </c>
+      <c r="G114" t="n">
+        <v>142.9133</v>
+      </c>
+      <c r="H114" t="n">
+        <v>412.5868</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.3123</v>
+      </c>
+      <c r="G115" t="n">
+        <v>150.4575</v>
+      </c>
+      <c r="H115" t="n">
+        <v>415.1101</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9732</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.9354</v>
+      </c>
+      <c r="G116" t="n">
+        <v>268.2256</v>
+      </c>
+      <c r="H116" t="n">
+        <v>718.4478</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9363</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.9425</v>
+      </c>
+      <c r="G117" t="n">
+        <v>360.4412</v>
+      </c>
+      <c r="H117" t="n">
+        <v>721.1728000000001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.2937</v>
+      </c>
+      <c r="G118" t="n">
+        <v>145.5803</v>
+      </c>
+      <c r="H118" t="n">
+        <v>402.5937</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.3494</v>
+      </c>
+      <c r="G119" t="n">
+        <v>152.8505</v>
+      </c>
+      <c r="H119" t="n">
+        <v>439.09</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.3817</v>
+      </c>
+      <c r="G120" t="n">
+        <v>217.232</v>
+      </c>
+      <c r="H120" t="n">
+        <v>458.9253</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.3817</v>
+      </c>
+      <c r="G121" t="n">
+        <v>217.232</v>
+      </c>
+      <c r="H121" t="n">
+        <v>458.9253</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="G122" t="n">
+        <v>145.2857</v>
+      </c>
+      <c r="H122" t="n">
+        <v>399.3493</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.3485</v>
+      </c>
+      <c r="G123" t="n">
+        <v>152.8511</v>
+      </c>
+      <c r="H123" t="n">
+        <v>438.5531</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="G124" t="n">
+        <v>143.908</v>
+      </c>
+      <c r="H124" t="n">
+        <v>415.6278</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.3016</v>
+      </c>
+      <c r="G125" t="n">
+        <v>140.516</v>
+      </c>
+      <c r="H125" t="n">
+        <v>407.9868</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.3811</v>
+      </c>
+      <c r="G126" t="n">
+        <v>155.7285</v>
+      </c>
+      <c r="H126" t="n">
+        <v>458.5686</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>total.carotene</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="G127" t="n">
+        <v>145.4663</v>
+      </c>
+      <c r="H127" t="n">
+        <v>418.2538</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9828</v>
+        <v>0.9796</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2969</v>
+        <v>0.6966</v>
       </c>
       <c r="G2" t="n">
-        <v>151.0448</v>
+        <v>159.6168</v>
       </c>
       <c r="H2" t="n">
-        <v>404.7857</v>
+        <v>399.7287</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9885</v>
+        <v>0.9869</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3176</v>
+        <v>0.655</v>
       </c>
       <c r="G3" t="n">
-        <v>146.0298</v>
+        <v>145.3953</v>
       </c>
       <c r="H3" t="n">
-        <v>418.6153</v>
+        <v>426.2733</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9806</v>
+        <v>0.9167</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3879</v>
+        <v>0.5815</v>
       </c>
       <c r="G4" t="n">
-        <v>167.9224</v>
+        <v>298.4713</v>
       </c>
       <c r="H4" t="n">
-        <v>462.6603</v>
+        <v>469.4879</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8154</v>
+        <v>0.7748</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9867</v>
+        <v>0.0243</v>
       </c>
       <c r="G5" t="n">
-        <v>466.8552</v>
+        <v>505.8633</v>
       </c>
       <c r="H5" t="n">
-        <v>737.8918</v>
+        <v>716.8484999999999</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.819</v>
+        <v>0.7724</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9649</v>
+        <v>0.0369</v>
       </c>
       <c r="G6" t="n">
-        <v>464.6835</v>
+        <v>502.5891</v>
       </c>
       <c r="H6" t="n">
-        <v>729.6925</v>
+        <v>712.2089</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9714</v>
+        <v>0.9473</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4082</v>
+        <v>0.5484</v>
       </c>
       <c r="G7" t="n">
-        <v>191.6005</v>
+        <v>243.0291</v>
       </c>
       <c r="H7" t="n">
-        <v>474.5844</v>
+        <v>487.676</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9704</v>
+        <v>0.9373</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4233</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>193.6418</v>
+        <v>263.2898</v>
       </c>
       <c r="H8" t="n">
-        <v>483.3017</v>
+        <v>480.8331</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9823</v>
+        <v>0.9798</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2928</v>
+        <v>0.6801</v>
       </c>
       <c r="G9" t="n">
-        <v>167.0875</v>
+        <v>173.3913</v>
       </c>
       <c r="H9" t="n">
-        <v>401.9541</v>
+        <v>410.4743</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9801</v>
+        <v>0.9691</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4429</v>
+        <v>0.5572</v>
       </c>
       <c r="G10" t="n">
-        <v>163.8578</v>
+        <v>190.9189</v>
       </c>
       <c r="H10" t="n">
-        <v>494.3625</v>
+        <v>482.933</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9291</v>
+        <v>0.9697</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4424</v>
+        <v>0.5544</v>
       </c>
       <c r="G11" t="n">
-        <v>285.0217</v>
+        <v>188.9336</v>
       </c>
       <c r="H11" t="n">
-        <v>494.101</v>
+        <v>484.4305</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9287</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4417</v>
+        <v>0.5546</v>
       </c>
       <c r="G12" t="n">
-        <v>285.0983</v>
+        <v>189.9167</v>
       </c>
       <c r="H12" t="n">
-        <v>493.7026</v>
+        <v>484.3453</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9391</v>
+        <v>0.9695</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4441</v>
+        <v>0.5524</v>
       </c>
       <c r="G13" t="n">
-        <v>265.9858</v>
+        <v>189.1789</v>
       </c>
       <c r="H13" t="n">
-        <v>495.0347</v>
+        <v>485.5587</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9283</v>
+        <v>0.9697</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4427</v>
+        <v>0.5589</v>
       </c>
       <c r="G14" t="n">
-        <v>286.1997</v>
+        <v>188.809</v>
       </c>
       <c r="H14" t="n">
-        <v>494.2503</v>
+        <v>482.016</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9287</v>
+        <v>0.9687</v>
       </c>
       <c r="F15" t="n">
-        <v>1.443</v>
+        <v>0.5588</v>
       </c>
       <c r="G15" t="n">
-        <v>285.0607</v>
+        <v>191.0258</v>
       </c>
       <c r="H15" t="n">
-        <v>494.4172</v>
+        <v>482.0637</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9288</v>
+        <v>0.9692</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4426</v>
+        <v>0.5551</v>
       </c>
       <c r="G16" t="n">
-        <v>285.1617</v>
+        <v>189.7581</v>
       </c>
       <c r="H16" t="n">
-        <v>494.2206</v>
+        <v>484.0516</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9696</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4429</v>
+        <v>0.5518</v>
       </c>
       <c r="G17" t="n">
-        <v>286.7732</v>
+        <v>188.7577</v>
       </c>
       <c r="H17" t="n">
-        <v>494.3753</v>
+        <v>485.8455</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9769</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3067</v>
+        <v>0.6804</v>
       </c>
       <c r="G18" t="n">
-        <v>141.3703</v>
+        <v>164.067</v>
       </c>
       <c r="H18" t="n">
-        <v>411.4052</v>
+        <v>410.2631</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9861</v>
+        <v>0.9791</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3079</v>
+        <v>0.6614</v>
       </c>
       <c r="G19" t="n">
-        <v>138.7135</v>
+        <v>164.771</v>
       </c>
       <c r="H19" t="n">
-        <v>412.1816</v>
+        <v>422.2798</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9848</v>
+        <v>0.969</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2969</v>
+        <v>0.6791</v>
       </c>
       <c r="G20" t="n">
-        <v>142.464</v>
+        <v>188.9428</v>
       </c>
       <c r="H20" t="n">
-        <v>404.7815</v>
+        <v>411.1412</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9859</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2945</v>
+        <v>0.6873</v>
       </c>
       <c r="G21" t="n">
-        <v>138.6819</v>
+        <v>162.5762</v>
       </c>
       <c r="H21" t="n">
-        <v>403.1424</v>
+        <v>405.8309</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9855</v>
+        <v>0.9815</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2908</v>
+        <v>0.6755</v>
       </c>
       <c r="G22" t="n">
-        <v>138.8886</v>
+        <v>152.4957</v>
       </c>
       <c r="H22" t="n">
-        <v>400.5622</v>
+        <v>413.3869</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9842</v>
+        <v>0.9809</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2949</v>
+        <v>0.6657</v>
       </c>
       <c r="G23" t="n">
-        <v>142.2974</v>
+        <v>156.3705</v>
       </c>
       <c r="H23" t="n">
-        <v>403.3844</v>
+        <v>419.5806</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9842</v>
+        <v>0.9808</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3042</v>
+        <v>0.6663</v>
       </c>
       <c r="G24" t="n">
-        <v>144.5674</v>
+        <v>157.7413</v>
       </c>
       <c r="H24" t="n">
-        <v>409.7005</v>
+        <v>419.2038</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9843</v>
+        <v>0.9819</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3</v>
+        <v>0.6792</v>
       </c>
       <c r="G25" t="n">
-        <v>143.795</v>
+        <v>150.2839</v>
       </c>
       <c r="H25" t="n">
-        <v>406.8922</v>
+        <v>411.0277</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9867</v>
+        <v>0.9705</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3017</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>136.8078</v>
+        <v>184.0616</v>
       </c>
       <c r="H26" t="n">
-        <v>408.0235</v>
+        <v>405.3522</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9849</v>
+        <v>0.9777</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3121</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>144.5872</v>
+        <v>161.1985</v>
       </c>
       <c r="H27" t="n">
-        <v>415.0324</v>
+        <v>398.739</v>
       </c>
     </row>
     <row r="28">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9855</v>
+        <v>0.9794</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3067</v>
+        <v>0.6919</v>
       </c>
       <c r="G28" t="n">
-        <v>136.8713</v>
+        <v>157.443</v>
       </c>
       <c r="H28" t="n">
-        <v>411.3966</v>
+        <v>402.8178</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9795</v>
+        <v>0.9809</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3101</v>
+        <v>0.6714</v>
       </c>
       <c r="G29" t="n">
-        <v>161.4232</v>
+        <v>157.9892</v>
       </c>
       <c r="H29" t="n">
-        <v>413.6655</v>
+        <v>416.0129</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9787</v>
+        <v>0.9754</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3045</v>
+        <v>0.6976</v>
       </c>
       <c r="G30" t="n">
-        <v>165.5457</v>
+        <v>169.4364</v>
       </c>
       <c r="H30" t="n">
-        <v>409.9493</v>
+        <v>399.0944</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9851</v>
+        <v>0.9806</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3007</v>
+        <v>0.6758</v>
       </c>
       <c r="G31" t="n">
-        <v>141.6466</v>
+        <v>155.0227</v>
       </c>
       <c r="H31" t="n">
-        <v>407.3619</v>
+        <v>413.2513</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9857</v>
+        <v>0.9837</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3014</v>
+        <v>0.6766</v>
       </c>
       <c r="G32" t="n">
-        <v>139.7082</v>
+        <v>149.0339</v>
       </c>
       <c r="H32" t="n">
-        <v>407.7976</v>
+        <v>412.6801</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.986</v>
+        <v>0.9808</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2995</v>
+        <v>0.6736</v>
       </c>
       <c r="G33" t="n">
-        <v>138.5481</v>
+        <v>152.9751</v>
       </c>
       <c r="H33" t="n">
-        <v>406.513</v>
+        <v>414.6311</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9856</v>
+        <v>0.9795</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3572</v>
+        <v>0.6411</v>
       </c>
       <c r="G34" t="n">
-        <v>155.2315</v>
+        <v>173.5125</v>
       </c>
       <c r="H34" t="n">
-        <v>443.9462</v>
+        <v>434.7954</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9781</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3408</v>
+        <v>0.6296</v>
       </c>
       <c r="G35" t="n">
-        <v>146.2623</v>
+        <v>180.2527</v>
       </c>
       <c r="H35" t="n">
-        <v>433.6415</v>
+        <v>441.6612</v>
       </c>
     </row>
     <row r="36">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9873</v>
+        <v>0.9859</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3081</v>
+        <v>0.6663</v>
       </c>
       <c r="G36" t="n">
-        <v>144.3525</v>
+        <v>148.0195</v>
       </c>
       <c r="H36" t="n">
-        <v>412.3493</v>
+        <v>419.2226</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9777</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2979</v>
+        <v>0.6822</v>
       </c>
       <c r="G37" t="n">
-        <v>171.108</v>
+        <v>171.3699</v>
       </c>
       <c r="H37" t="n">
-        <v>405.4825</v>
+        <v>409.1507</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9875</v>
+        <v>0.9777</v>
       </c>
       <c r="F38" t="n">
-        <v>1.291</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>137.0224</v>
+        <v>175.73</v>
       </c>
       <c r="H38" t="n">
-        <v>400.7396</v>
+        <v>402.7898</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9859</v>
+        <v>0.9774</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2924</v>
+        <v>0.6867</v>
       </c>
       <c r="G39" t="n">
-        <v>144.6516</v>
+        <v>172.6515</v>
       </c>
       <c r="H39" t="n">
-        <v>401.6865</v>
+        <v>406.2134</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9866</v>
+        <v>0.9805</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2866</v>
+        <v>0.6818</v>
       </c>
       <c r="G40" t="n">
-        <v>144.7637</v>
+        <v>157.3601</v>
       </c>
       <c r="H40" t="n">
-        <v>397.671</v>
+        <v>409.3629</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9858</v>
+        <v>0.9796</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3581</v>
+        <v>0.6393</v>
       </c>
       <c r="G41" t="n">
-        <v>154.7251</v>
+        <v>173.5669</v>
       </c>
       <c r="H41" t="n">
-        <v>444.5496</v>
+        <v>435.8333</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9873</v>
+        <v>0.9777</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3417</v>
+        <v>0.6286</v>
       </c>
       <c r="G42" t="n">
-        <v>146.5081</v>
+        <v>180.8582</v>
       </c>
       <c r="H42" t="n">
-        <v>434.2128</v>
+        <v>442.2629</v>
       </c>
     </row>
     <row r="43">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9875</v>
+        <v>0.9859</v>
       </c>
       <c r="F43" t="n">
-        <v>1.309</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>143.5189</v>
+        <v>149.234</v>
       </c>
       <c r="H43" t="n">
-        <v>412.937</v>
+        <v>420.1887</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9817</v>
+        <v>0.9782</v>
       </c>
       <c r="F44" t="n">
-        <v>1.2947</v>
+        <v>0.6816</v>
       </c>
       <c r="G44" t="n">
-        <v>170.2936</v>
+        <v>169.826</v>
       </c>
       <c r="H44" t="n">
-        <v>403.2844</v>
+        <v>409.5366</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.987</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2918</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>137.114</v>
+        <v>152.4043</v>
       </c>
       <c r="H45" t="n">
-        <v>401.2891</v>
+        <v>397.4108</v>
       </c>
     </row>
     <row r="46">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9861</v>
+        <v>0.9817</v>
       </c>
       <c r="F46" t="n">
-        <v>1.2932</v>
+        <v>0.6921</v>
       </c>
       <c r="G46" t="n">
-        <v>145.0911</v>
+        <v>158.0492</v>
       </c>
       <c r="H46" t="n">
-        <v>402.2137</v>
+        <v>402.7317</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9852</v>
+        <v>0.9807</v>
       </c>
       <c r="F47" t="n">
-        <v>1.2852</v>
+        <v>0.6788</v>
       </c>
       <c r="G47" t="n">
-        <v>151.9777</v>
+        <v>155.9232</v>
       </c>
       <c r="H47" t="n">
-        <v>396.7468</v>
+        <v>411.278</v>
       </c>
     </row>
     <row r="48">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9859</v>
+        <v>0.9851</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3196</v>
+        <v>0.6474</v>
       </c>
       <c r="G48" t="n">
-        <v>150.0634</v>
+        <v>153.8619</v>
       </c>
       <c r="H48" t="n">
-        <v>419.9648</v>
+        <v>430.9583</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9873</v>
+        <v>0.9822</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3011</v>
+        <v>0.6738</v>
       </c>
       <c r="G49" t="n">
-        <v>143.4427</v>
+        <v>161.1998</v>
       </c>
       <c r="H49" t="n">
-        <v>407.6489</v>
+        <v>414.507</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9301</v>
+        <v>0.9224</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8236</v>
+        <v>0.0822</v>
       </c>
       <c r="G50" t="n">
-        <v>352.6602</v>
+        <v>368.8824</v>
       </c>
       <c r="H50" t="n">
-        <v>674.1663</v>
+        <v>695.2587</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8789</v>
+        <v>0.8721</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8737</v>
+        <v>0.0345</v>
       </c>
       <c r="G51" t="n">
-        <v>432.7913</v>
+        <v>452.6996</v>
       </c>
       <c r="H51" t="n">
-        <v>694.3619</v>
+        <v>713.0891</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9724</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8722</v>
+        <v>0.0394</v>
       </c>
       <c r="G52" t="n">
-        <v>253.2649</v>
+        <v>453.3951</v>
       </c>
       <c r="H52" t="n">
-        <v>693.7646999999999</v>
+        <v>711.2853</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9739</v>
+        <v>0.8928</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8533</v>
+        <v>0.0838</v>
       </c>
       <c r="G53" t="n">
-        <v>255.6</v>
+        <v>437.0711</v>
       </c>
       <c r="H53" t="n">
-        <v>686.2117</v>
+        <v>694.6535</v>
       </c>
     </row>
     <row r="54">
@@ -2142,16 +2142,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9133</v>
+        <v>0.9117</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8369</v>
+        <v>0.1225</v>
       </c>
       <c r="G54" t="n">
-        <v>374.3873</v>
+        <v>378.0736</v>
       </c>
       <c r="H54" t="n">
-        <v>679.5921</v>
+        <v>679.8415</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9092</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9067</v>
+        <v>0.0108</v>
       </c>
       <c r="G55" t="n">
-        <v>413.3794</v>
+        <v>459.822</v>
       </c>
       <c r="H55" t="n">
-        <v>707.3315</v>
+        <v>721.796</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9735</v>
+        <v>0.9176</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9141</v>
+        <v>0.0211</v>
       </c>
       <c r="G56" t="n">
-        <v>256.6694</v>
+        <v>445.5897</v>
       </c>
       <c r="H56" t="n">
-        <v>710.2431</v>
+        <v>718.0271</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9065</v>
+        <v>0.9069</v>
       </c>
       <c r="F57" t="n">
-        <v>1.9093</v>
+        <v>0.044</v>
       </c>
       <c r="G57" t="n">
-        <v>404.1177</v>
+        <v>431.5822</v>
       </c>
       <c r="H57" t="n">
-        <v>708.3645</v>
+        <v>709.5817</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.822</v>
+        <v>0.8074</v>
       </c>
       <c r="F58" t="n">
-        <v>1.9752</v>
+        <v>0.0361</v>
       </c>
       <c r="G58" t="n">
-        <v>461.5699</v>
+        <v>473.8794</v>
       </c>
       <c r="H58" t="n">
-        <v>733.5714</v>
+        <v>712.513</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8248</v>
+        <v>0.8081</v>
       </c>
       <c r="F59" t="n">
-        <v>1.9691</v>
+        <v>0.0361</v>
       </c>
       <c r="G59" t="n">
-        <v>460.0352</v>
+        <v>473.118</v>
       </c>
       <c r="H59" t="n">
-        <v>731.2899</v>
+        <v>712.5305</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8256</v>
+        <v>0.769</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9695</v>
+        <v>0.0394</v>
       </c>
       <c r="G60" t="n">
-        <v>460.9157</v>
+        <v>503.5839</v>
       </c>
       <c r="H60" t="n">
-        <v>731.4295</v>
+        <v>711.3038</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8242</v>
+        <v>0.7692</v>
       </c>
       <c r="F61" t="n">
-        <v>1.9706</v>
+        <v>0.0404</v>
       </c>
       <c r="G61" t="n">
-        <v>460.2261</v>
+        <v>503.0508</v>
       </c>
       <c r="H61" t="n">
-        <v>731.8599</v>
+        <v>710.9102</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8781</v>
+        <v>0.8329</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9196</v>
+        <v>0.0654</v>
       </c>
       <c r="G62" t="n">
-        <v>422.9497</v>
+        <v>478.5413</v>
       </c>
       <c r="H62" t="n">
-        <v>712.3815</v>
+        <v>701.6088</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8344</v>
+        <v>0.8581</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9077</v>
+        <v>0.0793</v>
       </c>
       <c r="G63" t="n">
-        <v>469.1378</v>
+        <v>437.0749</v>
       </c>
       <c r="H63" t="n">
-        <v>707.7419</v>
+        <v>696.3674</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8279</v>
+        <v>0.8573</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9141</v>
+        <v>0.0936</v>
       </c>
       <c r="G64" t="n">
-        <v>469.5093</v>
+        <v>436.4129</v>
       </c>
       <c r="H64" t="n">
-        <v>710.25</v>
+        <v>690.9371</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8244</v>
+        <v>0.8467</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9211</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>470.1753</v>
+        <v>441.8413</v>
       </c>
       <c r="H65" t="n">
-        <v>712.9307</v>
+        <v>689.773</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.8842</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9158</v>
+        <v>0.0398</v>
       </c>
       <c r="G66" t="n">
-        <v>324.3285</v>
+        <v>458.5946</v>
       </c>
       <c r="H66" t="n">
-        <v>710.8966</v>
+        <v>711.1458</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.899</v>
+        <v>0.8831</v>
       </c>
       <c r="F67" t="n">
-        <v>1.913</v>
+        <v>0.0599</v>
       </c>
       <c r="G67" t="n">
-        <v>431.4987</v>
+        <v>459.4187</v>
       </c>
       <c r="H67" t="n">
-        <v>709.819</v>
+        <v>703.6787</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9563</v>
+        <v>0.9036</v>
       </c>
       <c r="F68" t="n">
-        <v>1.9164</v>
+        <v>0.0444</v>
       </c>
       <c r="G68" t="n">
-        <v>312.2426</v>
+        <v>437.6918</v>
       </c>
       <c r="H68" t="n">
-        <v>711.1324</v>
+        <v>709.4388</v>
       </c>
     </row>
     <row r="69">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9829</v>
+        <v>0.9777</v>
       </c>
       <c r="F69" t="n">
-        <v>1.3022</v>
+        <v>0.6672</v>
       </c>
       <c r="G69" t="n">
-        <v>150.4635</v>
+        <v>163.8428</v>
       </c>
       <c r="H69" t="n">
-        <v>408.3429</v>
+        <v>418.6363</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9812</v>
+        <v>0.979</v>
       </c>
       <c r="F70" t="n">
-        <v>1.2841</v>
+        <v>0.6918</v>
       </c>
       <c r="G70" t="n">
-        <v>157.9104</v>
+        <v>159.2537</v>
       </c>
       <c r="H70" t="n">
-        <v>395.9731</v>
+        <v>402.9204</v>
       </c>
     </row>
     <row r="71">
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9829</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3144</v>
+        <v>0.6671</v>
       </c>
       <c r="G71" t="n">
-        <v>147.7907</v>
+        <v>161.1704</v>
       </c>
       <c r="H71" t="n">
-        <v>416.5199</v>
+        <v>418.724</v>
       </c>
     </row>
     <row r="72">
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9839</v>
+        <v>0.979</v>
       </c>
       <c r="F72" t="n">
-        <v>1.2892</v>
+        <v>0.6814</v>
       </c>
       <c r="G72" t="n">
-        <v>141.3213</v>
+        <v>159.5248</v>
       </c>
       <c r="H72" t="n">
-        <v>399.48</v>
+        <v>409.644</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9788</v>
+        <v>0.9738</v>
       </c>
       <c r="F73" t="n">
-        <v>1.345</v>
+        <v>0.6123</v>
       </c>
       <c r="G73" t="n">
-        <v>173.3679</v>
+        <v>192.9622</v>
       </c>
       <c r="H73" t="n">
-        <v>436.3506</v>
+        <v>451.8621</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9857</v>
+        <v>0.9738</v>
       </c>
       <c r="F74" t="n">
-        <v>1.325</v>
+        <v>0.6732</v>
       </c>
       <c r="G74" t="n">
-        <v>147.4815</v>
+        <v>180.8131</v>
       </c>
       <c r="H74" t="n">
-        <v>423.4993</v>
+        <v>414.8796</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9832</v>
+        <v>0.9574</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3685</v>
+        <v>0.6137</v>
       </c>
       <c r="G75" t="n">
-        <v>152.3315</v>
+        <v>220.8537</v>
       </c>
       <c r="H75" t="n">
-        <v>450.9167</v>
+        <v>451.085</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9832</v>
+        <v>0.9574</v>
       </c>
       <c r="F76" t="n">
-        <v>1.3685</v>
+        <v>0.6137</v>
       </c>
       <c r="G76" t="n">
-        <v>152.3315</v>
+        <v>220.8537</v>
       </c>
       <c r="H76" t="n">
-        <v>450.9167</v>
+        <v>451.085</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8519</v>
+        <v>0.8414</v>
       </c>
       <c r="F77" t="n">
-        <v>1.9101</v>
+        <v>0.0375</v>
       </c>
       <c r="G77" t="n">
-        <v>442.5775</v>
+        <v>446.3254</v>
       </c>
       <c r="H77" t="n">
-        <v>708.6772</v>
+        <v>712.0074</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.848</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>1.9141</v>
+        <v>0.0451</v>
       </c>
       <c r="G78" t="n">
-        <v>447.6067</v>
+        <v>448.4394</v>
       </c>
       <c r="H78" t="n">
-        <v>710.2478</v>
+        <v>709.1784</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8451</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>1.9166</v>
+        <v>0.0385</v>
       </c>
       <c r="G79" t="n">
-        <v>448.542</v>
+        <v>447.6651</v>
       </c>
       <c r="H79" t="n">
-        <v>711.2006</v>
+        <v>711.6237</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8484</v>
+        <v>0.8393</v>
       </c>
       <c r="F80" t="n">
-        <v>1.916</v>
+        <v>0.0441</v>
       </c>
       <c r="G80" t="n">
-        <v>446.8932</v>
+        <v>448.4011</v>
       </c>
       <c r="H80" t="n">
-        <v>710.9596</v>
+        <v>709.546</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8941</v>
+        <v>0.846</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9059</v>
+        <v>0.0274</v>
       </c>
       <c r="G81" t="n">
-        <v>418.4462</v>
+        <v>480.4995</v>
       </c>
       <c r="H81" t="n">
-        <v>707.0528</v>
+        <v>715.7068</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9182</v>
+        <v>0.8608</v>
       </c>
       <c r="F82" t="n">
-        <v>1.9036</v>
+        <v>0.027</v>
       </c>
       <c r="G82" t="n">
-        <v>376.5176</v>
+        <v>462.3792</v>
       </c>
       <c r="H82" t="n">
-        <v>706.1334000000001</v>
+        <v>715.8831</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9829</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3676</v>
+        <v>0.6103</v>
       </c>
       <c r="G83" t="n">
-        <v>152.3356</v>
+        <v>221.2607</v>
       </c>
       <c r="H83" t="n">
-        <v>450.3713</v>
+        <v>453.0422</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9829</v>
+        <v>0.9567</v>
       </c>
       <c r="F84" t="n">
-        <v>1.3674</v>
+        <v>0.6089</v>
       </c>
       <c r="G84" t="n">
-        <v>151.8918</v>
+        <v>222.3852</v>
       </c>
       <c r="H84" t="n">
-        <v>450.2881</v>
+        <v>453.8768</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9828</v>
+        <v>0.9571</v>
       </c>
       <c r="F85" t="n">
-        <v>1.369</v>
+        <v>0.6089</v>
       </c>
       <c r="G85" t="n">
-        <v>152.9954</v>
+        <v>221.1121</v>
       </c>
       <c r="H85" t="n">
-        <v>451.2231</v>
+        <v>453.8554</v>
       </c>
     </row>
     <row r="86">
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9843</v>
+        <v>0.9782</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3083</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>143.5673</v>
+        <v>161.1581</v>
       </c>
       <c r="H86" t="n">
-        <v>412.4611</v>
+        <v>410.5829</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.981</v>
+        <v>0.9782</v>
       </c>
       <c r="F87" t="n">
-        <v>1.3046</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>156.9673</v>
+        <v>160.5856</v>
       </c>
       <c r="H87" t="n">
-        <v>409.9681</v>
+        <v>409.2274</v>
       </c>
     </row>
     <row r="88">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.985</v>
+        <v>0.9775</v>
       </c>
       <c r="F88" t="n">
-        <v>1.2984</v>
+        <v>0.6768</v>
       </c>
       <c r="G88" t="n">
-        <v>137.8008</v>
+        <v>164.1864</v>
       </c>
       <c r="H88" t="n">
-        <v>405.7758</v>
+        <v>412.5723</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9852</v>
+        <v>0.9744</v>
       </c>
       <c r="F89" t="n">
-        <v>1.308</v>
+        <v>0.6912</v>
       </c>
       <c r="G89" t="n">
-        <v>141.0164</v>
+        <v>172.1771</v>
       </c>
       <c r="H89" t="n">
-        <v>412.2911</v>
+        <v>403.2801</v>
       </c>
     </row>
     <row r="90">
@@ -3294,16 +3294,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9875</v>
+        <v>0.9859</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3092</v>
+        <v>0.6644</v>
       </c>
       <c r="G90" t="n">
-        <v>143.6677</v>
+        <v>149.2259</v>
       </c>
       <c r="H90" t="n">
-        <v>413.0624</v>
+        <v>420.4237</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9817</v>
+        <v>0.9782</v>
       </c>
       <c r="F91" t="n">
-        <v>1.2947</v>
+        <v>0.6816</v>
       </c>
       <c r="G91" t="n">
-        <v>170.2936</v>
+        <v>169.9432</v>
       </c>
       <c r="H91" t="n">
-        <v>403.2827</v>
+        <v>409.5382</v>
       </c>
     </row>
     <row r="92">
@@ -3358,16 +3358,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.985</v>
+        <v>0.9775</v>
       </c>
       <c r="F92" t="n">
-        <v>1.2984</v>
+        <v>0.6768</v>
       </c>
       <c r="G92" t="n">
-        <v>137.8008</v>
+        <v>164.1864</v>
       </c>
       <c r="H92" t="n">
-        <v>405.7758</v>
+        <v>412.5723</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9817</v>
+        <v>0.9782</v>
       </c>
       <c r="F93" t="n">
-        <v>1.2947</v>
+        <v>0.6816</v>
       </c>
       <c r="G93" t="n">
-        <v>170.2936</v>
+        <v>169.9432</v>
       </c>
       <c r="H93" t="n">
-        <v>403.2827</v>
+        <v>409.5382</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9806</v>
+        <v>0.9167</v>
       </c>
       <c r="F94" t="n">
-        <v>1.3879</v>
+        <v>0.5815</v>
       </c>
       <c r="G94" t="n">
-        <v>167.9224</v>
+        <v>298.4713</v>
       </c>
       <c r="H94" t="n">
-        <v>462.6603</v>
+        <v>469.4879</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9287</v>
+        <v>0.9203</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0797</v>
+        <v>-0.0982</v>
       </c>
       <c r="G95" t="n">
-        <v>378.3759</v>
+        <v>381.7566</v>
       </c>
       <c r="H95" t="n">
-        <v>771.8746</v>
+        <v>760.5232999999999</v>
       </c>
     </row>
     <row r="96">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9808</v>
+        <v>0.9747</v>
       </c>
       <c r="F96" t="n">
-        <v>1.393</v>
+        <v>0.583</v>
       </c>
       <c r="G96" t="n">
-        <v>167.8609</v>
+        <v>181.5196</v>
       </c>
       <c r="H96" t="n">
-        <v>465.708</v>
+        <v>468.6539</v>
       </c>
     </row>
     <row r="97">
@@ -3518,16 +3518,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9811</v>
+        <v>0.9747</v>
       </c>
       <c r="F97" t="n">
-        <v>1.3894</v>
+        <v>0.5838</v>
       </c>
       <c r="G97" t="n">
-        <v>168.1098</v>
+        <v>181.169</v>
       </c>
       <c r="H97" t="n">
-        <v>463.5503</v>
+        <v>468.2008</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9849</v>
+        <v>0.975</v>
       </c>
       <c r="F98" t="n">
-        <v>1.302</v>
+        <v>0.657</v>
       </c>
       <c r="G98" t="n">
-        <v>143.7823</v>
+        <v>174.7036</v>
       </c>
       <c r="H98" t="n">
-        <v>408.251</v>
+        <v>425.0496</v>
       </c>
     </row>
     <row r="99">
@@ -3582,16 +3582,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9789</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>1.2828</v>
+        <v>0.6825</v>
       </c>
       <c r="G99" t="n">
-        <v>163.5888</v>
+        <v>171.4864</v>
       </c>
       <c r="H99" t="n">
-        <v>395.0298</v>
+        <v>408.9101</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9779</v>
+        <v>0.9774</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3075</v>
+        <v>0.6764</v>
       </c>
       <c r="G100" t="n">
-        <v>165.7757</v>
+        <v>164.1018</v>
       </c>
       <c r="H100" t="n">
-        <v>411.9262</v>
+        <v>412.844</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9755</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3028</v>
+        <v>0.6733</v>
       </c>
       <c r="G101" t="n">
-        <v>173.8032</v>
+        <v>171.8256</v>
       </c>
       <c r="H101" t="n">
-        <v>408.7666</v>
+        <v>414.8331</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.983</v>
+        <v>0.9629</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3069</v>
+        <v>0.6773</v>
       </c>
       <c r="G102" t="n">
-        <v>149.5473</v>
+        <v>206.3158</v>
       </c>
       <c r="H102" t="n">
-        <v>411.5037</v>
+        <v>412.2595</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9843</v>
+        <v>0.977</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3207</v>
+        <v>0.6653</v>
       </c>
       <c r="G103" t="n">
-        <v>149.4075</v>
+        <v>170.5633</v>
       </c>
       <c r="H103" t="n">
-        <v>420.7085</v>
+        <v>419.8327</v>
       </c>
     </row>
     <row r="104">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9832</v>
+        <v>0.978</v>
       </c>
       <c r="F104" t="n">
-        <v>1.3038</v>
+        <v>0.6581</v>
       </c>
       <c r="G104" t="n">
-        <v>151.8478</v>
+        <v>165.5251</v>
       </c>
       <c r="H104" t="n">
-        <v>409.4548</v>
+        <v>424.3661</v>
       </c>
     </row>
     <row r="105">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9838</v>
+        <v>0.9785</v>
       </c>
       <c r="F105" t="n">
-        <v>1.2937</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="G105" t="n">
-        <v>145.5803</v>
+        <v>160.7428</v>
       </c>
       <c r="H105" t="n">
-        <v>402.5937</v>
+        <v>413.1601</v>
       </c>
     </row>
     <row r="106">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9852</v>
+        <v>0.9774</v>
       </c>
       <c r="F106" t="n">
-        <v>1.2764</v>
+        <v>0.6882</v>
       </c>
       <c r="G106" t="n">
-        <v>140.4119</v>
+        <v>163.5253</v>
       </c>
       <c r="H106" t="n">
-        <v>390.5261</v>
+        <v>405.2564</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9786</v>
+        <v>0.9784</v>
       </c>
       <c r="F107" t="n">
-        <v>1.2864</v>
+        <v>0.6726</v>
       </c>
       <c r="G107" t="n">
-        <v>165.4651</v>
+        <v>160.7102</v>
       </c>
       <c r="H107" t="n">
-        <v>397.5491</v>
+        <v>415.2655</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9774</v>
+        <v>0.9706</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3819</v>
+        <v>0.6116</v>
       </c>
       <c r="G108" t="n">
-        <v>189.3776</v>
+        <v>205.4325</v>
       </c>
       <c r="H108" t="n">
-        <v>459.0692</v>
+        <v>452.3062</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9861</v>
+        <v>0.974</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3478</v>
+        <v>0.6542</v>
       </c>
       <c r="G109" t="n">
-        <v>153.1223</v>
+        <v>192.2429</v>
       </c>
       <c r="H109" t="n">
-        <v>438.1152</v>
+        <v>426.7882</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9875</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3108</v>
+        <v>0.6866</v>
       </c>
       <c r="G110" t="n">
-        <v>141.9579</v>
+        <v>156.0198</v>
       </c>
       <c r="H110" t="n">
-        <v>414.1135</v>
+        <v>406.2957</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9863</v>
+        <v>0.9811</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3128</v>
+        <v>0.667</v>
       </c>
       <c r="G111" t="n">
-        <v>143.9735</v>
+        <v>159.0536</v>
       </c>
       <c r="H111" t="n">
-        <v>415.4574</v>
+        <v>418.821</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9774</v>
+        <v>0.9706</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3813</v>
+        <v>0.6141</v>
       </c>
       <c r="G112" t="n">
-        <v>188.8464</v>
+        <v>205.2554</v>
       </c>
       <c r="H112" t="n">
-        <v>458.684</v>
+        <v>450.8252</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9858</v>
+        <v>0.9737</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3494</v>
+        <v>0.6535</v>
       </c>
       <c r="G113" t="n">
-        <v>152.8505</v>
+        <v>193.2131</v>
       </c>
       <c r="H113" t="n">
-        <v>439.09</v>
+        <v>427.2189</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9872</v>
+        <v>0.9838</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3085</v>
+        <v>0.6838</v>
       </c>
       <c r="G114" t="n">
-        <v>142.9133</v>
+        <v>155.1371</v>
       </c>
       <c r="H114" t="n">
-        <v>412.5868</v>
+        <v>408.0677</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.986</v>
+        <v>0.9758</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3123</v>
+        <v>0.6666</v>
       </c>
       <c r="G115" t="n">
-        <v>150.4575</v>
+        <v>183.8234</v>
       </c>
       <c r="H115" t="n">
-        <v>415.1101</v>
+        <v>419.022</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9732</v>
+        <v>0.8156</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9354</v>
+        <v>-0.0003</v>
       </c>
       <c r="G116" t="n">
-        <v>268.2256</v>
+        <v>499.2352</v>
       </c>
       <c r="H116" t="n">
-        <v>718.4478</v>
+        <v>725.8332</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9363</v>
+        <v>0.8358</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9425</v>
+        <v>-0.017</v>
       </c>
       <c r="G117" t="n">
-        <v>360.4412</v>
+        <v>486.4816</v>
       </c>
       <c r="H117" t="n">
-        <v>721.1728000000001</v>
+        <v>731.8601</v>
       </c>
     </row>
     <row r="118">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9838</v>
+        <v>0.9785</v>
       </c>
       <c r="F118" t="n">
-        <v>1.2937</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>145.5803</v>
+        <v>160.7428</v>
       </c>
       <c r="H118" t="n">
-        <v>402.5937</v>
+        <v>413.1601</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9858</v>
+        <v>0.9737</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3494</v>
+        <v>0.6535</v>
       </c>
       <c r="G119" t="n">
-        <v>152.8505</v>
+        <v>193.2131</v>
       </c>
       <c r="H119" t="n">
-        <v>439.09</v>
+        <v>427.2189</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9627</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>217.232</v>
+        <v>300.8531</v>
       </c>
       <c r="H120" t="n">
-        <v>458.9253</v>
+        <v>474.7076</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9627</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="G121" t="n">
-        <v>217.232</v>
+        <v>300.8531</v>
       </c>
       <c r="H121" t="n">
-        <v>458.9253</v>
+        <v>474.7076</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9837</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>1.289</v>
+        <v>0.6874</v>
       </c>
       <c r="G122" t="n">
-        <v>145.2857</v>
+        <v>165.3057</v>
       </c>
       <c r="H122" t="n">
-        <v>399.3493</v>
+        <v>405.7386</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9858</v>
+        <v>0.9737</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3485</v>
+        <v>0.6535</v>
       </c>
       <c r="G123" t="n">
-        <v>152.8511</v>
+        <v>193.1923</v>
       </c>
       <c r="H123" t="n">
-        <v>438.5531</v>
+        <v>427.1937</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9809</v>
       </c>
       <c r="F124" t="n">
-        <v>1.313</v>
+        <v>0.6902</v>
       </c>
       <c r="G124" t="n">
-        <v>143.908</v>
+        <v>161.7816</v>
       </c>
       <c r="H124" t="n">
-        <v>415.6278</v>
+        <v>403.9136</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9869</v>
+        <v>0.9812</v>
       </c>
       <c r="F125" t="n">
-        <v>1.3016</v>
+        <v>0.7062</v>
       </c>
       <c r="G125" t="n">
-        <v>140.516</v>
+        <v>153.6666</v>
       </c>
       <c r="H125" t="n">
-        <v>407.9868</v>
+        <v>393.3528</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9853</v>
+        <v>0.9523</v>
       </c>
       <c r="F126" t="n">
-        <v>1.3811</v>
+        <v>0.5919</v>
       </c>
       <c r="G126" t="n">
-        <v>155.7285</v>
+        <v>248.8596</v>
       </c>
       <c r="H126" t="n">
-        <v>458.5686</v>
+        <v>463.6003</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9766</v>
       </c>
       <c r="F127" t="n">
-        <v>1.317</v>
+        <v>0.6913</v>
       </c>
       <c r="G127" t="n">
-        <v>145.4663</v>
+        <v>181.3171</v>
       </c>
       <c r="H127" t="n">
-        <v>418.2538</v>
+        <v>403.2425</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9069</v>
+        <v>0.9063</v>
       </c>
       <c r="F57" t="n">
         <v>0.044</v>
       </c>
       <c r="G57" t="n">
-        <v>431.5822</v>
+        <v>431.9993</v>
       </c>
       <c r="H57" t="n">
         <v>709.5817</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
